--- a/Balanzas/2026/08/Balanza.xlsx
+++ b/Balanzas/2026/08/Balanza.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\dashboard-financiero\Balanzas\2026\08\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD07BD85-64D6-4990-B76E-9E0510EF077A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68319EFF-BDA3-4B53-8B6E-2F502C92BD2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CIVLAT" sheetId="2" r:id="rId1"/>
+    <sheet name="CIVMEX" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12509" uniqueCount="3802">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12782" uniqueCount="3812">
   <si>
     <t>C u e n t a</t>
   </si>
@@ -11431,6 +11432,36 @@
   </si>
   <si>
     <t xml:space="preserve">Sumas Iguales: </t>
+  </si>
+  <si>
+    <t>101-00002-003-0006</t>
+  </si>
+  <si>
+    <t>Banorte 0277994660</t>
+  </si>
+  <si>
+    <t>101-00008-012-0000</t>
+  </si>
+  <si>
+    <t>ISR a Favor</t>
+  </si>
+  <si>
+    <t>101-00008-012-0005</t>
+  </si>
+  <si>
+    <t>ISR 2023</t>
+  </si>
+  <si>
+    <t>101-00008-012-0060</t>
+  </si>
+  <si>
+    <t>ISR 2024</t>
+  </si>
+  <si>
+    <t>Civ Comerc de Infraest Vial SA</t>
+  </si>
+  <si>
+    <t>411-26777-004-0468</t>
   </si>
 </sst>
 </file>
@@ -93222,4 +93253,1834 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FAB74CE-A7A4-42D3-B99D-E6D9C2D95DFE}">
+  <dimension ref="A1:H70"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="6">
+        <v>29184.91</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="6">
+        <v>65.38</v>
+      </c>
+      <c r="F2" s="6">
+        <v>269.69</v>
+      </c>
+      <c r="G2" s="6">
+        <v>28980.6</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="7">
+        <v>27886.52</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="7">
+        <v>0</v>
+      </c>
+      <c r="F3" s="7">
+        <v>237</v>
+      </c>
+      <c r="G3" s="7">
+        <v>27649.52</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="6">
+        <v>27886.52</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6">
+        <v>237</v>
+      </c>
+      <c r="G4" s="6">
+        <v>27649.52</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>3802</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>3803</v>
+      </c>
+      <c r="C5" s="6">
+        <v>27886.52</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="6">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6">
+        <v>237</v>
+      </c>
+      <c r="G5" s="6">
+        <v>27649.52</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1224</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="7">
+        <v>0</v>
+      </c>
+      <c r="F6" s="7">
+        <v>0</v>
+      </c>
+      <c r="G6" s="7">
+        <v>1224</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="C7" s="6">
+        <v>132</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6">
+        <v>132</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>3804</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>3805</v>
+      </c>
+      <c r="C8" s="6">
+        <v>1092</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0</v>
+      </c>
+      <c r="G8" s="6">
+        <v>1092</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>3806</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>3807</v>
+      </c>
+      <c r="C9" s="6">
+        <v>896</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6">
+        <v>896</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>3808</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>3809</v>
+      </c>
+      <c r="C10" s="6">
+        <v>196</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6">
+        <v>0</v>
+      </c>
+      <c r="G10" s="6">
+        <v>196</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C11" s="7">
+        <v>5.84</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="7">
+        <v>32.69</v>
+      </c>
+      <c r="F11" s="7">
+        <v>32.69</v>
+      </c>
+      <c r="G11" s="7">
+        <v>5.84</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="C12" s="6">
+        <v>5.84</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="6">
+        <v>32.69</v>
+      </c>
+      <c r="F12" s="6">
+        <v>32.69</v>
+      </c>
+      <c r="G12" s="6">
+        <v>5.84</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C13" s="7">
+        <v>68.55</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="7">
+        <v>32.69</v>
+      </c>
+      <c r="F13" s="7">
+        <v>0</v>
+      </c>
+      <c r="G13" s="7">
+        <v>101.24</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="C14" s="6">
+        <v>68.55</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="6">
+        <v>32.69</v>
+      </c>
+      <c r="F14" s="6">
+        <v>0</v>
+      </c>
+      <c r="G14" s="6">
+        <v>101.24</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="C15" s="6">
+        <v>66370.7</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0</v>
+      </c>
+      <c r="F15" s="6">
+        <v>0</v>
+      </c>
+      <c r="G15" s="6">
+        <v>66370.7</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="C16" s="9">
+        <v>-66370.7</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0</v>
+      </c>
+      <c r="F16" s="6">
+        <v>0</v>
+      </c>
+      <c r="G16" s="9">
+        <v>-66370.7</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="C17" s="6">
+        <v>589000</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0</v>
+      </c>
+      <c r="F17" s="6">
+        <v>0</v>
+      </c>
+      <c r="G17" s="6">
+        <v>589000</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="C18" s="9">
+        <v>-589000</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0</v>
+      </c>
+      <c r="F18" s="6">
+        <v>0</v>
+      </c>
+      <c r="G18" s="9">
+        <v>-589000</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="C19" s="6">
+        <v>642281.54</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0</v>
+      </c>
+      <c r="F19" s="6">
+        <v>4310.3500000000004</v>
+      </c>
+      <c r="G19" s="6">
+        <v>637971.18999999994</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C20" s="7">
+        <v>642281.54</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0</v>
+      </c>
+      <c r="F20" s="7">
+        <v>4310.3500000000004</v>
+      </c>
+      <c r="G20" s="7">
+        <v>637971.18999999994</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="C21" s="6">
+        <v>1034483</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0</v>
+      </c>
+      <c r="F21" s="6">
+        <v>0</v>
+      </c>
+      <c r="G21" s="6">
+        <v>1034483</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="C22" s="9">
+        <v>-392201.46</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="6">
+        <v>0</v>
+      </c>
+      <c r="F22" s="6">
+        <v>4310.3500000000004</v>
+      </c>
+      <c r="G22" s="9">
+        <v>-396511.81</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="6">
+        <v>1003.29</v>
+      </c>
+      <c r="E23" s="6">
+        <v>237</v>
+      </c>
+      <c r="F23" s="6">
+        <v>237</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="6">
+        <v>1003.29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="7">
+        <v>0</v>
+      </c>
+      <c r="E24" s="7">
+        <v>237</v>
+      </c>
+      <c r="F24" s="7">
+        <v>237</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="6">
+        <v>0</v>
+      </c>
+      <c r="E25" s="6">
+        <v>237</v>
+      </c>
+      <c r="F25" s="6">
+        <v>237</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H25" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="6">
+        <v>0</v>
+      </c>
+      <c r="E26" s="6">
+        <v>237</v>
+      </c>
+      <c r="F26" s="6">
+        <v>237</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="11">
+        <v>-14.08</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0</v>
+      </c>
+      <c r="F27" s="7">
+        <v>0</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H27" s="11">
+        <v>-14.08</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>721</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>722</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="9">
+        <v>-14.08</v>
+      </c>
+      <c r="E28" s="6">
+        <v>0</v>
+      </c>
+      <c r="F28" s="6">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H28" s="9">
+        <v>-14.08</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>723</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>724</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="9">
+        <v>-14.08</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0</v>
+      </c>
+      <c r="F29" s="6">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" s="9">
+        <v>-14.08</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="7">
+        <v>1017.37</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0</v>
+      </c>
+      <c r="F30" s="7">
+        <v>0</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H30" s="7">
+        <v>1017.37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>753</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>754</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="6">
+        <v>100000</v>
+      </c>
+      <c r="E31" s="6">
+        <v>0</v>
+      </c>
+      <c r="F31" s="6">
+        <v>0</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H31" s="6">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="7">
+        <v>100000</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0</v>
+      </c>
+      <c r="F32" s="7">
+        <v>0</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="7">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>756</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>757</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="6">
+        <v>100000</v>
+      </c>
+      <c r="E33" s="6">
+        <v>0</v>
+      </c>
+      <c r="F33" s="6">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H33" s="6">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>3810</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="6">
+        <v>80000</v>
+      </c>
+      <c r="E34" s="6">
+        <v>0</v>
+      </c>
+      <c r="F34" s="6">
+        <v>0</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H34" s="6">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="6">
+        <v>20000</v>
+      </c>
+      <c r="E35" s="6">
+        <v>0</v>
+      </c>
+      <c r="F35" s="6">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H35" s="6">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>781</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="6">
+        <v>614302.82999999996</v>
+      </c>
+      <c r="E36" s="6">
+        <v>0</v>
+      </c>
+      <c r="F36" s="6">
+        <v>0</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H36" s="6">
+        <v>614302.82999999996</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="7">
+        <v>50000</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0</v>
+      </c>
+      <c r="F37" s="7">
+        <v>0</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H37" s="7">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>786</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="6">
+        <v>50000</v>
+      </c>
+      <c r="E38" s="6">
+        <v>0</v>
+      </c>
+      <c r="F38" s="6">
+        <v>0</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H38" s="6">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="7">
+        <v>564302.82999999996</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0</v>
+      </c>
+      <c r="F39" s="7">
+        <v>0</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H39" s="7">
+        <v>564302.82999999996</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="s">
+        <v>791</v>
+      </c>
+      <c r="B40" s="10">
+        <v>2015</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="6">
+        <v>225174.02</v>
+      </c>
+      <c r="E40" s="6">
+        <v>0</v>
+      </c>
+      <c r="F40" s="6">
+        <v>0</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H40" s="6">
+        <v>225174.02</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="B41" s="10">
+        <v>2016</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="6">
+        <v>511831.66</v>
+      </c>
+      <c r="E41" s="6">
+        <v>0</v>
+      </c>
+      <c r="F41" s="6">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H41" s="6">
+        <v>511831.66</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="5" t="s">
+        <v>793</v>
+      </c>
+      <c r="B42" s="10">
+        <v>2017</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="6">
+        <v>97369.77</v>
+      </c>
+      <c r="E42" s="6">
+        <v>0</v>
+      </c>
+      <c r="F42" s="6">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H42" s="6">
+        <v>97369.77</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
+        <v>794</v>
+      </c>
+      <c r="B43" s="10">
+        <v>2018</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="6">
+        <v>853349.62</v>
+      </c>
+      <c r="E43" s="6">
+        <v>0</v>
+      </c>
+      <c r="F43" s="6">
+        <v>0</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H43" s="6">
+        <v>853349.62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="B44" s="10">
+        <v>2019</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="6">
+        <v>150792.1</v>
+      </c>
+      <c r="E44" s="6">
+        <v>0</v>
+      </c>
+      <c r="F44" s="6">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="6">
+        <v>150792.1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="B45" s="10">
+        <v>2020</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="6">
+        <v>168655.82</v>
+      </c>
+      <c r="E45" s="6">
+        <v>0</v>
+      </c>
+      <c r="F45" s="6">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="6">
+        <v>168655.82</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="5" t="s">
+        <v>797</v>
+      </c>
+      <c r="B46" s="10">
+        <v>2021</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="6">
+        <v>55766.31</v>
+      </c>
+      <c r="E46" s="6">
+        <v>0</v>
+      </c>
+      <c r="F46" s="6">
+        <v>0</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H46" s="6">
+        <v>55766.31</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="5" t="s">
+        <v>798</v>
+      </c>
+      <c r="B47" s="10">
+        <v>2022</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="6">
+        <v>82850.03</v>
+      </c>
+      <c r="E47" s="6">
+        <v>0</v>
+      </c>
+      <c r="F47" s="6">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="6">
+        <v>82850.03</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="s">
+        <v>799</v>
+      </c>
+      <c r="B48" s="10">
+        <v>2023</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="9">
+        <v>-1523688.81</v>
+      </c>
+      <c r="E48" s="6">
+        <v>0</v>
+      </c>
+      <c r="F48" s="6">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H48" s="9">
+        <v>-1523688.81</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="5" t="s">
+        <v>800</v>
+      </c>
+      <c r="B49" s="10">
+        <v>2024</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="6">
+        <v>2289.4699999999998</v>
+      </c>
+      <c r="E49" s="6">
+        <v>0</v>
+      </c>
+      <c r="F49" s="6">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H49" s="6">
+        <v>2289.4699999999998</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
+        <v>801</v>
+      </c>
+      <c r="B50" s="10">
+        <v>2025</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="9">
+        <v>-60087.16</v>
+      </c>
+      <c r="E50" s="6">
+        <v>0</v>
+      </c>
+      <c r="F50" s="6">
+        <v>0</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H50" s="9">
+        <v>-60087.16</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="5" t="s">
+        <v>808</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>809</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="6">
+        <v>25862.07</v>
+      </c>
+      <c r="E51" s="6">
+        <v>0</v>
+      </c>
+      <c r="F51" s="6">
+        <v>0</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H51" s="6">
+        <v>25862.07</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="5" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>973</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="6">
+        <v>25862.07</v>
+      </c>
+      <c r="E52" s="6">
+        <v>0</v>
+      </c>
+      <c r="F52" s="6">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H52" s="6">
+        <v>25862.07</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="5" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="6">
+        <v>25862.07</v>
+      </c>
+      <c r="E53" s="6">
+        <v>0</v>
+      </c>
+      <c r="F53" s="6">
+        <v>0</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H53" s="6">
+        <v>25862.07</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="5" t="s">
+        <v>3811</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>520</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="6">
+        <v>25862.07</v>
+      </c>
+      <c r="E54" s="6">
+        <v>0</v>
+      </c>
+      <c r="F54" s="6">
+        <v>0</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H54" s="6">
+        <v>25862.07</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="5" t="s">
+        <v>3687</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>3688</v>
+      </c>
+      <c r="C55" s="6">
+        <v>39506.36</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="6">
+        <v>204.31</v>
+      </c>
+      <c r="F55" s="6">
+        <v>0</v>
+      </c>
+      <c r="G55" s="6">
+        <v>39710.67</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>3689</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>3610</v>
+      </c>
+      <c r="C56" s="7">
+        <v>39506.36</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="7">
+        <v>204.31</v>
+      </c>
+      <c r="F56" s="7">
+        <v>0</v>
+      </c>
+      <c r="G56" s="7">
+        <v>39710.67</v>
+      </c>
+      <c r="H56" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="5" t="s">
+        <v>3728</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>3729</v>
+      </c>
+      <c r="C57" s="6">
+        <v>1448.28</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="6">
+        <v>204.31</v>
+      </c>
+      <c r="F57" s="6">
+        <v>0</v>
+      </c>
+      <c r="G57" s="6">
+        <v>1652.59</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="5" t="s">
+        <v>3730</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>3731</v>
+      </c>
+      <c r="C58" s="6">
+        <v>1448.28</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="6">
+        <v>204.31</v>
+      </c>
+      <c r="F58" s="6">
+        <v>0</v>
+      </c>
+      <c r="G58" s="6">
+        <v>1652.59</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="5" t="s">
+        <v>3746</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>3534</v>
+      </c>
+      <c r="C59" s="6">
+        <v>1286</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="6">
+        <v>0</v>
+      </c>
+      <c r="F59" s="6">
+        <v>0</v>
+      </c>
+      <c r="G59" s="6">
+        <v>1286</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="5" t="s">
+        <v>3747</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>3748</v>
+      </c>
+      <c r="C60" s="6">
+        <v>105.35</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="6">
+        <v>0</v>
+      </c>
+      <c r="F60" s="6">
+        <v>0</v>
+      </c>
+      <c r="G60" s="6">
+        <v>105.35</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="5" t="s">
+        <v>3749</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="C61" s="6">
+        <v>105.35</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" s="6">
+        <v>0</v>
+      </c>
+      <c r="F61" s="6">
+        <v>0</v>
+      </c>
+      <c r="G61" s="6">
+        <v>105.35</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="5" t="s">
+        <v>3754</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="C62" s="6">
+        <v>36666.730000000003</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="6">
+        <v>0</v>
+      </c>
+      <c r="F62" s="6">
+        <v>0</v>
+      </c>
+      <c r="G62" s="6">
+        <v>36666.730000000003</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="5" t="s">
+        <v>3770</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>3771</v>
+      </c>
+      <c r="C63" s="6">
+        <v>30192.38</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E63" s="6">
+        <v>4310.3500000000004</v>
+      </c>
+      <c r="F63" s="6">
+        <v>0</v>
+      </c>
+      <c r="G63" s="6">
+        <v>34502.730000000003</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>3772</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>3610</v>
+      </c>
+      <c r="C64" s="7">
+        <v>30192.38</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E64" s="7">
+        <v>4310.3500000000004</v>
+      </c>
+      <c r="F64" s="7">
+        <v>0</v>
+      </c>
+      <c r="G64" s="7">
+        <v>34502.730000000003</v>
+      </c>
+      <c r="H64" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="5" t="s">
+        <v>3779</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>3780</v>
+      </c>
+      <c r="C65" s="6">
+        <v>30192.38</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E65" s="6">
+        <v>4310.3500000000004</v>
+      </c>
+      <c r="F65" s="6">
+        <v>0</v>
+      </c>
+      <c r="G65" s="6">
+        <v>34502.730000000003</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="5" t="s">
+        <v>3781</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="C66" s="6">
+        <v>30192.38</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="6">
+        <v>4310.3500000000004</v>
+      </c>
+      <c r="F66" s="6">
+        <v>0</v>
+      </c>
+      <c r="G66" s="6">
+        <v>34502.730000000003</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="5" t="s">
+        <v>3782</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>3783</v>
+      </c>
+      <c r="C67" s="6">
+        <v>3</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E67" s="6">
+        <v>0</v>
+      </c>
+      <c r="F67" s="6">
+        <v>0</v>
+      </c>
+      <c r="G67" s="6">
+        <v>3</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>3784</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>3783</v>
+      </c>
+      <c r="C68" s="7">
+        <v>3</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E68" s="7">
+        <v>0</v>
+      </c>
+      <c r="F68" s="7">
+        <v>0</v>
+      </c>
+      <c r="G68" s="7">
+        <v>3</v>
+      </c>
+      <c r="H68" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="5" t="s">
+        <v>3790</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>3791</v>
+      </c>
+      <c r="C69" s="6">
+        <v>3</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E69" s="6">
+        <v>0</v>
+      </c>
+      <c r="F69" s="6">
+        <v>0</v>
+      </c>
+      <c r="G69" s="6">
+        <v>3</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="5" t="s">
+        <v>3792</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>3793</v>
+      </c>
+      <c r="C70" s="6">
+        <v>3</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E70" s="6">
+        <v>0</v>
+      </c>
+      <c r="F70" s="6">
+        <v>0</v>
+      </c>
+      <c r="G70" s="6">
+        <v>3</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>